--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][Raw]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][Raw]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9777255654335022</v>
+        <v>0.9776562452316284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4605384469032288</v>
+        <v>0.4714111685752869</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7815066576004028</v>
+        <v>0.7785250544548035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002149472711607814</v>
+        <v>0.001974816899746656</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9348286390304565</v>
+        <v>0.9402144551277161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008455741219222546</v>
+        <v>0.01507196202874184</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,10 +545,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9669052958488464</v>
+        <v>0.9452182650566101</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8098796010017395</v>
+        <v>0.4525154232978821</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9764994978904724</v>
+        <v>0.975343644618988</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4155288338661194</v>
+        <v>0.3891586661338806</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8069238066673279</v>
+        <v>0.8231856822967529</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004517089109867811</v>
+        <v>0.007410064339637756</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9759982228279114</v>
+        <v>0.9659888744354248</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3980652689933777</v>
+        <v>0.1668571680784225</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,10 +621,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9235619306564331</v>
+        <v>0.9443874955177307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2182402014732361</v>
+        <v>0.440746545791626</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -630,16 +642,16 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9194156527519226</v>
+        <v>0.9198673367500305</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002246136777102947</v>
+        <v>0.002618040423840284</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,14 +659,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8700027465820312</v>
+        <v>0.8830476403236389</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03374403715133667</v>
+        <v>0.0526948906481266</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9796485304832458</v>
+        <v>0.9803968071937561</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5372365117073059</v>
+        <v>0.5819981694221497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8468347787857056</v>
+        <v>0.8372335433959961</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01566833071410656</v>
+        <v>0.01151254400610924</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9860172867774963</v>
+        <v>0.9881565570831299</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8143159151077271</v>
+        <v>0.8997973203659058</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9354228973388672</v>
+        <v>0.9454593658447266</v>
       </c>
       <c r="I8" t="n">
-        <v>0.328283816576004</v>
+        <v>0.455972820520401</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9477657079696655</v>
+        <v>0.9527269005775452</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02763689868152142</v>
+        <v>0.04765783995389938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,14 +773,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8970822691917419</v>
+        <v>0.8761652112007141</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08590099960565567</v>
+        <v>0.04160477221012115</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>0.981963574886322</v>
+        <v>0.9821984171867371</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6372089982032776</v>
+        <v>0.6599615812301636</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8737266659736633</v>
+        <v>0.8630889654159546</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03828641399741173</v>
+        <v>0.02674806490540504</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
         <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9644301533699036</v>
+        <v>0.9640246629714966</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1362610161304474</v>
+        <v>0.1386824995279312</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,10 +849,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8656286597251892</v>
+        <v>0.8602744340896606</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02912170439958572</v>
+        <v>0.02435400523245335</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9408503770828247</v>
+        <v>0.939103901386261</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01455964427441359</v>
+        <v>0.01364310178905725</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9567946195602417</v>
+        <v>0.9917526841163635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6369038224220276</v>
+        <v>0.9998558163642883</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9740140438079834</v>
+        <v>0.9635753035545349</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3344157636165619</v>
+        <v>0.1329189538955688</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +925,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9717602133750916</v>
+        <v>0.9714609980583191</v>
       </c>
       <c r="I13" t="n">
-        <v>0.883213996887207</v>
+        <v>0.8790730237960815</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -934,16 +946,16 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9591304063796997</v>
+        <v>0.9567168354988098</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08173888176679611</v>
+        <v>0.06941349804401398</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9681615829467773</v>
+        <v>0.9657715559005737</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8299565315246582</v>
+        <v>0.7912693619728088</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9666529893875122</v>
+        <v>0.9703673720359802</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1686151623725891</v>
+        <v>0.2504382431507111</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9566186666488647</v>
+        <v>0.9505805969238281</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6338837146759033</v>
+        <v>0.5336419939994812</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1010,27 +1022,27 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9600149989128113</v>
+        <v>0.9513541460037231</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08902185410261154</v>
+        <v>0.04190682247281075</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9050058126449585</v>
+        <v>0.9285819530487061</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1135258674621582</v>
+        <v>0.2598526775836945</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
         <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9713810086250305</v>
+        <v>0.9748460054397583</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2631781399250031</v>
+        <v>0.3729407489299774</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,10 +1077,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.9088820219039917</v>
+        <v>0.8858464956283569</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1301686018705368</v>
+        <v>0.05804945901036263</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9420580863952637</v>
+        <v>0.9475314021110535</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01626349054276943</v>
+        <v>0.02937151305377483</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.9405872225761414</v>
+        <v>0.9642485380172729</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3898119032382965</v>
+        <v>0.765692412853241</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1124,16 +1136,16 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9249276518821716</v>
+        <v>0.9253300428390503</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003569931490346789</v>
+        <v>0.004124054685235023</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1141,10 +1153,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.962131679058075</v>
+        <v>0.9347178339958191</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7293885350227356</v>
+        <v>0.3205597400665283</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1162,27 +1174,27 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9546979069709778</v>
+        <v>0.9262440204620361</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05336563289165497</v>
+        <v>0.004454728215932846</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9307331442832947</v>
+        <v>0.9531539678573608</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2798415124416351</v>
+        <v>0.5754213333129883</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9778735637664795</v>
+        <v>0.9737612009048462</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4661866426467896</v>
+        <v>0.3394327163696289</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,10 +1229,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.9480111002922058</v>
+        <v>0.9468438625335693</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4936891496181488</v>
+        <v>0.4761843979358673</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1238,16 +1250,16 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
         <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9486257433891296</v>
+        <v>0.9488530158996582</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02996483258903027</v>
+        <v>0.03319576755166054</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.9019361734390259</v>
+        <v>0.9462131857872009</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1018844023346901</v>
+        <v>0.4669020175933838</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9739953875541687</v>
+        <v>0.9689067602157593</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3338596820831299</v>
+        <v>0.2189928740262985</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,10 +1305,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.936290979385376</v>
+        <v>0.9321997165679932</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3380131423473358</v>
+        <v>0.2942577004432678</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1314,16 +1326,16 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" t="n">
         <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>0.939240038394928</v>
+        <v>0.9173998832702637</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0125730000436306</v>
+        <v>0.002140087774023414</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8427433967590332</v>
+        <v>0.8344883918762207</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01373023726046085</v>
+        <v>0.01055262517184019</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" t="n">
         <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9816207885742188</v>
+        <v>0.9811294674873352</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6220461130142212</v>
+        <v>0.6133819818496704</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8059711456298828</v>
+        <v>0.7898139357566833</v>
       </c>
       <c r="I25" t="n">
-        <v>0.004390137270092964</v>
+        <v>0.002728952327743173</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1390,16 +1402,16 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9636076092720032</v>
+        <v>0.9759244322776794</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1258920431137085</v>
+        <v>0.4087590277194977</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1407,10 +1419,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.9671204686164856</v>
+        <v>0.9697777628898621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8133620619773865</v>
+        <v>0.8547500371932983</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1428,27 +1440,27 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" t="n">
         <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>0.957334041595459</v>
+        <v>0.9531645774841309</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06874491274356842</v>
+        <v>0.04965701326727867</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.9447805881500244</v>
+        <v>0.9328793883323669</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4462867379188538</v>
+        <v>0.3011617958545685</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" t="n">
         <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9847010970115662</v>
+        <v>0.9849199652671814</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7586812376976013</v>
+        <v>0.7780958414077759</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8941916227340698</v>
+        <v>0.9149783849716187</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07762646675109863</v>
+        <v>0.161421149969101</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1504,16 +1516,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9752745628356934</v>
+        <v>0.9740145206451416</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3738369345664978</v>
+        <v>0.3470318615436554</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1521,10 +1533,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9285612106323242</v>
+        <v>0.9211674332618713</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2596660256385803</v>
+        <v>0.2006908059120178</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" t="n">
         <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9280633330345154</v>
+        <v>0.9354075193405151</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004671273753046989</v>
+        <v>0.009826114401221275</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,10 +1571,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8206319808959961</v>
+        <v>0.8338613510131836</v>
       </c>
       <c r="I30" t="n">
-        <v>0.006848654244095087</v>
+        <v>0.01034552231431007</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9909358024597168</v>
+        <v>0.9908750653266907</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9654970765113831</v>
+        <v>0.9668101072311401</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,14 +1609,14 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8874211311340332</v>
+        <v>0.8452941179275513</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0613076351583004</v>
+        <v>0.01490650977939367</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9070600867271423</v>
+        <v>0.900244414806366</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0008288208628073335</v>
+        <v>0.0005595964612439275</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8997809886932373</v>
+        <v>0.904624879360199</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09444289654493332</v>
+        <v>0.1120108142495155</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9889145493507385</v>
+        <v>0.9847490787506104</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9175970554351807</v>
+        <v>0.7708863615989685</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,10 +1685,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9323889017105103</v>
+        <v>0.9380198121070862</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2961649596691132</v>
+        <v>0.3581229448318481</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" t="n">
         <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9696298837661743</v>
+        <v>0.9746628403663635</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2235572040081024</v>
+        <v>0.3671057820320129</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.93468177318573</v>
+        <v>0.8870359063148499</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3201688528060913</v>
+        <v>0.06049333512783051</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
         <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>0.986498236656189</v>
+        <v>0.9862352609634399</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8336174488067627</v>
+        <v>0.8315146565437317</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.9592298865318298</v>
+        <v>0.9509702920913696</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6790118217468262</v>
+        <v>0.5398621559143066</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" t="n">
         <v>15</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9636836647987366</v>
+        <v>0.9551108479499817</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1268171221017838</v>
+        <v>0.05964289978146553</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9218748807907104</v>
+        <v>0.9268159866333008</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2057298719882965</v>
+        <v>0.2444339692592621</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
       </c>
       <c r="E37" t="n">
-        <v>0.980047881603241</v>
+        <v>0.9832718372344971</v>
       </c>
       <c r="F37" t="n">
-        <v>0.553985059261322</v>
+        <v>0.7070677876472473</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,10 +1837,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.9193157553672791</v>
+        <v>0.9234442710876465</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1880582273006439</v>
+        <v>0.2173444479703903</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9645741581916809</v>
+        <v>0.962122917175293</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1381604671478271</v>
+        <v>0.1158514246344566</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.916656494140625</v>
+        <v>0.9374076724052429</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1712576150894165</v>
+        <v>0.3508903384208679</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D39" t="n">
         <v>15</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9719812273979187</v>
+        <v>0.9630360007286072</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2781400084495544</v>
+        <v>0.1263107508420944</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,10 +1913,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.9282297492027283</v>
+        <v>0.9371575713157654</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2567073702812195</v>
+        <v>0.3479711413383484</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" t="n">
         <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>0.971818745136261</v>
+        <v>0.965525209903717</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2740175426006317</v>
+        <v>0.159745991230011</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,14 +1951,14 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8575466871261597</v>
+        <v>0.8851736783981323</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02224854566156864</v>
+        <v>0.0567125603556633</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" t="n">
         <v>15</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9649244546890259</v>
+        <v>0.9641540050506592</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1428889334201813</v>
+        <v>0.1403869390487671</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,10 +1989,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.9097050428390503</v>
+        <v>0.9013227820396423</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1340067684650421</v>
+        <v>0.0997074767947197</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1998,16 +2010,16 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="n">
         <v>15</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9517801403999329</v>
+        <v>0.9520158767700195</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04039044678211212</v>
+        <v>0.04458428546786308</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2015,10 +2027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.9675383567810059</v>
+        <v>0.9612973928451538</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8200755715370178</v>
+        <v>0.7149372696876526</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43" t="n">
         <v>15</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9513639211654663</v>
+        <v>0.9423010349273682</v>
       </c>
       <c r="F43" t="n">
-        <v>0.03882375359535217</v>
+        <v>0.01819585263729095</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9586631655693054</v>
+        <v>0.9603800773620605</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6691750288009644</v>
+        <v>0.6990033984184265</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D44" t="n">
         <v>15</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9619054198265076</v>
+        <v>0.9698691368103027</v>
       </c>
       <c r="F44" t="n">
-        <v>0.10683923214674</v>
+        <v>0.2392780184745789</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,10 +2103,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9193235635757446</v>
+        <v>0.910395085811615</v>
       </c>
       <c r="I44" t="n">
-        <v>0.188109964132309</v>
+        <v>0.1373119354248047</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D45" t="n">
         <v>15</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9789037108421326</v>
+        <v>0.9781994819641113</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5067077875137329</v>
+        <v>0.4923027455806732</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.9426016807556152</v>
+        <v>0.939875066280365</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4162139296531677</v>
+        <v>0.3808021247386932</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" t="n">
         <v>15</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9617195129394531</v>
+        <v>0.9593883752822876</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1049398630857468</v>
+        <v>0.08939871937036514</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,14 +2179,14 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8784757852554321</v>
+        <v>0.8956806063652039</v>
       </c>
       <c r="I46" t="n">
-        <v>0.04502734914422035</v>
+        <v>0.08178123831748962</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" t="n">
         <v>15</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9687967896461487</v>
+        <v>0.9718092083930969</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2066942602396011</v>
+        <v>0.2854042053222656</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9510074257850647</v>
+        <v>0.928768515586853</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5404564142227173</v>
+        <v>0.2615328133106232</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" t="n">
         <v>15</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9826997518539429</v>
+        <v>0.9823267459869385</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6699872612953186</v>
+        <v>0.6655898094177246</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9569322466850281</v>
+        <v>0.954992949962616</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6392697691917419</v>
+        <v>0.6061879992485046</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2264,16 +2276,16 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" t="n">
         <v>15</v>
       </c>
       <c r="E49" t="n">
-        <v>0.97380530834198</v>
+        <v>0.9760789275169373</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3282272517681122</v>
+        <v>0.4140950739383698</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2281,10 +2293,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9362370371818542</v>
+        <v>0.944752037525177</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3374017179012299</v>
+        <v>0.4458828270435333</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="n">
         <v>15</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9841853380203247</v>
+        <v>0.973937451839447</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7360949516296387</v>
+        <v>0.3447053730487823</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,10 +2331,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.9677075147628784</v>
+        <v>0.9736490249633789</v>
       </c>
       <c r="I50" t="n">
-        <v>0.822772741317749</v>
+        <v>0.907931387424469</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D51" t="n">
         <v>15</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9780245423316956</v>
+        <v>0.9782672524452209</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4719954431056976</v>
+        <v>0.4949471950531006</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.9542127847671509</v>
+        <v>0.9368873834609985</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5930541753768921</v>
+        <v>0.3448402583599091</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2378,16 +2390,16 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D52" t="n">
         <v>15</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9790434837341309</v>
+        <v>0.9757152199745178</v>
       </c>
       <c r="F52" t="n">
-        <v>0.512363076210022</v>
+        <v>0.401616632938385</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2395,10 +2407,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9311781525611877</v>
+        <v>0.9323054552078247</v>
       </c>
       <c r="I52" t="n">
-        <v>0.284147322177887</v>
+        <v>0.2953223586082458</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D53" t="n">
         <v>15</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9733990430831909</v>
+        <v>0.9640370607376099</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3164551556110382</v>
+        <v>0.1388450711965561</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,10 +2445,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.9125298261642456</v>
+        <v>0.9004253149032593</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1480607539415359</v>
+        <v>0.09660762548446655</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2454,16 +2466,16 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" t="n">
         <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9692427515983582</v>
+        <v>0.9740439653396606</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2155686616897583</v>
+        <v>0.3479235768318176</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8904450535774231</v>
+        <v>0.9118431806564331</v>
       </c>
       <c r="I54" t="n">
-        <v>0.068107008934021</v>
+        <v>0.144514724612236</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" t="n">
         <v>15</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9692435264587402</v>
+        <v>0.9693168997764587</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2155839949846268</v>
+        <v>0.2274371236562729</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9669391512870789</v>
+        <v>0.9591999650001526</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8104285001754761</v>
+        <v>0.6784926652908325</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2530,16 +2542,16 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" t="n">
         <v>15</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9680044651031494</v>
+        <v>0.9635382294654846</v>
       </c>
       <c r="F56" t="n">
-        <v>0.191761389374733</v>
+        <v>0.1324543356895447</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9286155700683594</v>
+        <v>0.942419707775116</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2601546049118042</v>
+        <v>0.4137739539146423</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" t="n">
         <v>15</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9739201068878174</v>
+        <v>0.9820519089698792</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3316205739974976</v>
+        <v>0.6535418033599854</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9668881297111511</v>
+        <v>0.9740765690803528</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8096007704734802</v>
+        <v>0.9131602644920349</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" t="n">
         <v>15</v>
       </c>
       <c r="E58" t="n">
-        <v>0.934789776802063</v>
+        <v>0.939415454864502</v>
       </c>
       <c r="F58" t="n">
-        <v>0.008426519110798836</v>
+        <v>0.0140290567651391</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.9678042531013489</v>
+        <v>0.9705212116241455</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8243104219436646</v>
+        <v>0.8656986951828003</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2644,16 +2656,16 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D59" t="n">
         <v>15</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9607791900634766</v>
+        <v>0.9566503763198853</v>
       </c>
       <c r="F59" t="n">
-        <v>0.09583549946546555</v>
+        <v>0.06897859275341034</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2661,10 +2673,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9363497495651245</v>
+        <v>0.9260452389717102</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3386805355548859</v>
+        <v>0.2379751056432724</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" t="n">
         <v>15</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9792755246162415</v>
+        <v>0.9808266758918762</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5218254327774048</v>
+        <v>0.600343644618988</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.9624332189559937</v>
+        <v>0.9332731366157532</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7345969080924988</v>
+        <v>0.3052270412445068</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2720,16 +2732,16 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" t="n">
         <v>15</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9454660415649414</v>
+        <v>0.939866304397583</v>
       </c>
       <c r="F61" t="n">
-        <v>0.02228979766368866</v>
+        <v>0.0146079221740365</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2737,10 +2749,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9691068530082703</v>
+        <v>0.9679515361785889</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8446135520935059</v>
+        <v>0.8266447186470032</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D62" t="n">
         <v>15</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8990428447723389</v>
+        <v>0.9073160290718079</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0004468260740395635</v>
+        <v>0.0009607925894670188</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2775,10 +2787,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.971549391746521</v>
+        <v>0.9732082486152649</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8803018927574158</v>
+        <v>0.9023942351341248</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D63" t="n">
         <v>15</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9862814545631409</v>
+        <v>0.9808830618858337</v>
       </c>
       <c r="F63" t="n">
-        <v>0.825000524520874</v>
+        <v>0.602764904499054</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,14 +2825,14 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.9242510199546814</v>
+        <v>0.8724623322486877</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2235552966594696</v>
+        <v>0.03667625039815903</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -2834,27 +2846,27 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D64" t="n">
         <v>15</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9497005939483643</v>
+        <v>0.9533194899559021</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0331626757979393</v>
+        <v>0.05038514360785484</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.9457429051399231</v>
+        <v>0.9430202841758728</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4600624144077301</v>
+        <v>0.4218702614307404</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2872,16 +2884,16 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D65" t="n">
         <v>15</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9558200240135193</v>
+        <v>0.9588272571563721</v>
       </c>
       <c r="F65" t="n">
-        <v>0.05943069979548454</v>
+        <v>0.0847678929567337</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2889,10 +2901,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.9854253530502319</v>
+        <v>0.9840261340141296</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9937797784805298</v>
+        <v>0.9897780418395996</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D66" t="n">
         <v>15</v>
       </c>
       <c r="E66" t="n">
-        <v>0.948363721370697</v>
+        <v>0.9386278986930847</v>
       </c>
       <c r="F66" t="n">
-        <v>0.02923488430678844</v>
+        <v>0.01307476870715618</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9894065260887146</v>
+        <v>0.9788213968276978</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9991271495819092</v>
+        <v>0.9608210325241089</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D67" t="n">
         <v>15</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9034207463264465</v>
+        <v>0.9080689549446106</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0006244175601750612</v>
+        <v>0.001018728711642325</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,10 +2977,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.9754060506820679</v>
+        <v>0.9815294146537781</v>
       </c>
       <c r="I67" t="n">
-        <v>0.928485095500946</v>
+        <v>0.9788661599159241</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D68" t="n">
         <v>15</v>
       </c>
       <c r="E68" t="n">
-        <v>0.958436131477356</v>
+        <v>0.9638205766677856</v>
       </c>
       <c r="F68" t="n">
-        <v>0.07644552737474442</v>
+        <v>0.1360349953174591</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9571875333786011</v>
+        <v>0.9577417373657227</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6436624526977539</v>
+        <v>0.653221607208252</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D69" t="n">
         <v>15</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9653988480567932</v>
+        <v>0.9758920073509216</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1495447307825089</v>
+        <v>0.4076475203037262</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.9673150181770325</v>
+        <v>0.9313855171203613</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8164958357810974</v>
+        <v>0.2861737608909607</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D70" t="n">
         <v>15</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9596315622329712</v>
+        <v>0.9546207785606384</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0857878103852272</v>
+        <v>0.05694960057735443</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.7862546443939209</v>
+        <v>0.7683253288269043</v>
       </c>
       <c r="I70" t="n">
-        <v>0.002462506061419845</v>
+        <v>0.001483167405240238</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D71" t="n">
         <v>15</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9306405186653137</v>
+        <v>0.9279716014862061</v>
       </c>
       <c r="F71" t="n">
-        <v>0.00584354205057025</v>
+        <v>0.005158466752618551</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.9283183813095093</v>
+        <v>0.912423849105835</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2574953734874725</v>
+        <v>0.1475075632333755</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3138,16 +3150,16 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D72" t="n">
         <v>15</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9219405055046082</v>
+        <v>0.9235192537307739</v>
       </c>
       <c r="F72" t="n">
-        <v>0.002773159183561802</v>
+        <v>0.00354292499832809</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.8359507322311401</v>
+        <v>0.7099636197090149</v>
       </c>
       <c r="I72" t="n">
-        <v>0.01105293910950422</v>
+        <v>0.0003182614163961262</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3176,16 +3188,16 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" t="n">
         <v>15</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9559279680252075</v>
+        <v>0.9545288681983948</v>
       </c>
       <c r="F73" t="n">
-        <v>0.06004990637302399</v>
+        <v>0.05645855888724327</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3193,10 +3205,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9531680345535278</v>
+        <v>0.9495872855186462</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5756531953811646</v>
+        <v>0.5179746150970459</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D74" t="n">
         <v>15</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9158623218536377</v>
+        <v>0.9133209586143494</v>
       </c>
       <c r="F74" t="n">
-        <v>0.001676495070569217</v>
+        <v>0.00154114025644958</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,10 +3243,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9023289084434509</v>
+        <v>0.8956488370895386</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1033033728599548</v>
+        <v>0.08169025927782059</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3252,16 +3264,16 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D75" t="n">
         <v>15</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9780437350273132</v>
+        <v>0.9847476482391357</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4727358520030975</v>
+        <v>0.770825982093811</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3269,10 +3281,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.839745044708252</v>
+        <v>0.8243693113327026</v>
       </c>
       <c r="I75" t="n">
-        <v>0.01247220300137997</v>
+        <v>0.007686707656830549</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D76" t="n">
         <v>15</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9693998694419861</v>
+        <v>0.9745080471038818</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2187783271074295</v>
+        <v>0.3622310161590576</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9518940448760986</v>
+        <v>0.9538381695747375</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5547628998756409</v>
+        <v>0.5867888331413269</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D77" t="n">
         <v>15</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9734058380126953</v>
+        <v>0.9744604825973511</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3166484534740448</v>
+        <v>0.3607431352138519</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9553622603416443</v>
+        <v>0.9629864096641541</v>
       </c>
       <c r="I77" t="n">
-        <v>0.612442672252655</v>
+        <v>0.7441256046295166</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3366,16 +3378,16 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D78" t="n">
         <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9466429948806763</v>
+        <v>0.9491511583328247</v>
       </c>
       <c r="F78" t="n">
-        <v>0.02487727254629135</v>
+        <v>0.03412759304046631</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3383,10 +3395,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.9737204313278198</v>
+        <v>0.9757643342018127</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9088146686553955</v>
+        <v>0.9323630928993225</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3404,16 +3416,16 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D79" t="n">
         <v>15</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9450643062591553</v>
+        <v>0.9470875859260559</v>
       </c>
       <c r="F79" t="n">
-        <v>0.02147205732762814</v>
+        <v>0.02819211222231388</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3421,10 +3433,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.9689531326293945</v>
+        <v>0.9671537280082703</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8422590494155884</v>
+        <v>0.8138989210128784</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D80" t="n">
         <v>15</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9778109192848206</v>
+        <v>0.980108380317688</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4637899696826935</v>
+        <v>0.5698133111000061</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9724315404891968</v>
+        <v>0.946071445941925</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8922892212867737</v>
+        <v>0.4648328125476837</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3480,16 +3492,16 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D81" t="n">
         <v>15</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9620743989944458</v>
+        <v>0.9634048342704773</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1085947751998901</v>
+        <v>0.1307942718267441</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3497,10 +3509,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.9399219751358032</v>
+        <v>0.9328477382659912</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3813897371292114</v>
+        <v>0.3008373379707336</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D82" t="n">
         <v>15</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9721508026123047</v>
+        <v>0.9735762476921082</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2825002372264862</v>
+        <v>0.3339700698852539</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.8973930478096008</v>
+        <v>0.9244116544723511</v>
       </c>
       <c r="I82" t="n">
-        <v>0.08684305846691132</v>
+        <v>0.2248119115829468</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D83" t="n">
         <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9879851937294006</v>
+        <v>0.9936205744743347</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8882741928100586</v>
+        <v>0.9953153133392334</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,10 +3585,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.9165404438972473</v>
+        <v>0.9145568609237671</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1705588549375534</v>
+        <v>0.1590389758348465</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D84" t="n">
         <v>15</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9874893426895142</v>
+        <v>0.986972987651825</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8710036277770996</v>
+        <v>0.8593736290931702</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.9051360487937927</v>
+        <v>0.9189887046813965</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1140484511852264</v>
+        <v>0.1859084814786911</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D85" t="n">
         <v>15</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9749113321304321</v>
+        <v>0.979250431060791</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3621156513690948</v>
+        <v>0.5342455506324768</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.9625968933105469</v>
+        <v>0.9404810667037964</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7374207377433777</v>
+        <v>0.3884576857089996</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3670,16 +3682,16 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D86" t="n">
         <v>15</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9519929885864258</v>
+        <v>0.9502773284912109</v>
       </c>
       <c r="F86" t="n">
-        <v>0.04121644422411919</v>
+        <v>0.03789838775992393</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3687,10 +3699,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.8308285474777222</v>
+        <v>0.8524963855743408</v>
       </c>
       <c r="I86" t="n">
-        <v>0.009403056465089321</v>
+        <v>0.0188418123871088</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D87" t="n">
         <v>15</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9657360911369324</v>
+        <v>0.963076651096344</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1544578075408936</v>
+        <v>0.126797690987587</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,10 +3737,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9712319374084473</v>
+        <v>0.9539287090301514</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8758634924888611</v>
+        <v>0.5883005261421204</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D88" t="n">
         <v>15</v>
       </c>
       <c r="E88" t="n">
-        <v>0.96256023645401</v>
+        <v>0.9598407745361328</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1138052716851234</v>
+        <v>0.09331656247377396</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,10 +3775,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.9542413949966431</v>
+        <v>0.9670513868331909</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5935336351394653</v>
+        <v>0.8122463822364807</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D89" t="n">
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9746536612510681</v>
+        <v>0.969222366809845</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3539789915084839</v>
+        <v>0.2254648506641388</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,14 +3813,14 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.9656122326850891</v>
+        <v>0.8432512283325195</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7886226177215576</v>
+        <v>0.01395635958760977</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D90" t="n">
         <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>0.983464777469635</v>
+        <v>0.9824310541152954</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7041370868682861</v>
+        <v>0.6701703667640686</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.956986665725708</v>
+        <v>0.948760986328125</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6402055025100708</v>
+        <v>0.505152702331543</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3860,16 +3872,16 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D91" t="n">
         <v>15</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9730618000030518</v>
+        <v>0.9703638553619385</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3069537580013275</v>
+        <v>0.2503582835197449</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.8949536681175232</v>
+        <v>0.9004921317100525</v>
       </c>
       <c r="I91" t="n">
-        <v>0.07972489297389984</v>
+        <v>0.0968349426984787</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3898,16 +3910,16 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D92" t="n">
         <v>15</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9410426616668701</v>
+        <v>0.9487436413764954</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01481785625219345</v>
+        <v>0.03286061808466911</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3915,10 +3927,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.8024524450302124</v>
+        <v>0.8008905053138733</v>
       </c>
       <c r="I92" t="n">
-        <v>0.003953234758228064</v>
+        <v>0.003774366807192564</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D93" t="n">
         <v>15</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9124960899353027</v>
+        <v>0.9152724742889404</v>
       </c>
       <c r="F93" t="n">
-        <v>0.001276297611184418</v>
+        <v>0.001801911625079811</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,14 +3965,14 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.903525710105896</v>
+        <v>0.779427707195282</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1077530160546303</v>
+        <v>0.002026033354923129</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D94" t="n">
         <v>15</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9379121661186218</v>
+        <v>0.9428909420967102</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01114882249385118</v>
+        <v>0.01919652335345745</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.8530389070510864</v>
+        <v>0.7982203960418701</v>
       </c>
       <c r="I94" t="n">
-        <v>0.01917975023388863</v>
+        <v>0.003488289657980204</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4012,16 +4024,16 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D95" t="n">
         <v>15</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9754636883735657</v>
+        <v>0.96241694688797</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3800573647022247</v>
+        <v>0.1191226989030838</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9447480440139771</v>
+        <v>0.9577969312667847</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4458261728286743</v>
+        <v>0.654175341129303</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4050,16 +4062,16 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D96" t="n">
         <v>15</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8942761421203613</v>
+        <v>0.891451358795166</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0003126267984043807</v>
+        <v>0.0002923095889855176</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4067,10 +4079,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.8736142516136169</v>
+        <v>0.8756272196769714</v>
       </c>
       <c r="I96" t="n">
-        <v>0.03814026713371277</v>
+        <v>0.04084765538573265</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D97" t="n">
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9332242012023926</v>
+        <v>0.9360936284065247</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0073335743509233</v>
+        <v>0.01043926179409027</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4105,14 +4117,14 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.9023923277854919</v>
+        <v>0.8583283424377441</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1035345494747162</v>
+        <v>0.02283147908747196</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4126,16 +4138,16 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D98" t="n">
         <v>15</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9466622471809387</v>
+        <v>0.9518511295318604</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02492208033800125</v>
+        <v>0.04390160739421844</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4143,10 +4155,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.9319753646850586</v>
+        <v>0.9416546225547791</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2920101284980774</v>
+        <v>0.4036329984664917</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D99" t="n">
         <v>15</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9463844299316406</v>
+        <v>0.9502238631248474</v>
       </c>
       <c r="F99" t="n">
-        <v>0.02428316697478294</v>
+        <v>0.03771009296178818</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,10 +4193,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.8758500814437866</v>
+        <v>0.8468320369720459</v>
       </c>
       <c r="I99" t="n">
-        <v>0.04115955159068108</v>
+        <v>0.01566692441701889</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4202,16 +4214,16 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D100" t="n">
         <v>15</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9576930999755859</v>
+        <v>0.9674492478370667</v>
       </c>
       <c r="F100" t="n">
-        <v>0.07116326689720154</v>
+        <v>0.1912831962108612</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.8517798185348511</v>
+        <v>0.8552055954933167</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01840503327548504</v>
+        <v>0.02059482038021088</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4240,16 +4252,16 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D101" t="n">
         <v>15</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9565012454986572</v>
+        <v>0.95562344789505</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0634513720870018</v>
+        <v>0.06259912252426147</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4257,10 +4269,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.954700767993927</v>
+        <v>0.9494036436080933</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6012559533119202</v>
+        <v>0.5151081085205078</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D102" t="n">
         <v>15</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9115110635757446</v>
+        <v>0.9153459668159485</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001179326209239662</v>
+        <v>0.001812600181438029</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.8717854619026184</v>
+        <v>0.7439197301864624</v>
       </c>
       <c r="I102" t="n">
-        <v>0.03584357723593712</v>
+        <v>0.000764053373131901</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D103" t="n">
         <v>15</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9744521379470825</v>
+        <v>0.9682872295379639</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3477171659469604</v>
+        <v>0.2067870050668716</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,10 +4345,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.9659303426742554</v>
+        <v>0.9678542613983154</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7939008474349976</v>
+        <v>0.8251039981842041</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4354,16 +4366,16 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D104" t="n">
         <v>15</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9353718161582947</v>
+        <v>0.9402953386306763</v>
       </c>
       <c r="F104" t="n">
-        <v>0.008875354193150997</v>
+        <v>0.01518199872225523</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4371,14 +4383,14 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.9466145038604736</v>
+        <v>0.8178412914276123</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4727947413921356</v>
+        <v>0.006286518648266792</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4392,27 +4404,27 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D105" t="n">
         <v>15</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9535999298095703</v>
+        <v>0.9675965905189514</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0480429083108902</v>
+        <v>0.1939273327589035</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9118710160255432</v>
+        <v>0.9173703193664551</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1446569561958313</v>
+        <v>0.1756178289651871</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4430,16 +4442,16 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D106" t="n">
         <v>15</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9718978404998779</v>
+        <v>0.9646064639091492</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2760175466537476</v>
+        <v>0.1465080231428146</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4447,10 +4459,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.8939737677574158</v>
+        <v>0.8972731828689575</v>
       </c>
       <c r="I106" t="n">
-        <v>0.07703699171543121</v>
+        <v>0.08647850900888443</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D107" t="n">
         <v>15</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9847215414047241</v>
+        <v>0.9849680066108704</v>
       </c>
       <c r="F107" t="n">
-        <v>0.7595694661140442</v>
+        <v>0.7801125049591064</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,14 +4497,14 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.8960937261581421</v>
+        <v>0.8635607957839966</v>
       </c>
       <c r="I107" t="n">
-        <v>0.08297399431467056</v>
+        <v>0.0271731223911047</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4506,16 +4518,16 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D108" t="n">
         <v>15</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9549750685691833</v>
+        <v>0.9562972187995911</v>
       </c>
       <c r="F108" t="n">
-        <v>0.05480231717228889</v>
+        <v>0.06671320647001266</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4523,10 +4535,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.9131615161895752</v>
+        <v>0.9479860663414001</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1513985991477966</v>
+        <v>0.4933094084262848</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D109" t="n">
         <v>15</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9054928421974182</v>
+        <v>0.9116599559783936</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0007332513341680169</v>
+        <v>0.001350592356175184</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9592345356941223</v>
+        <v>0.9596197605133057</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6790932416915894</v>
+        <v>0.6857865452766418</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D110" t="n">
         <v>15</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9911367893218994</v>
+        <v>0.9804779887199402</v>
       </c>
       <c r="F110" t="n">
-        <v>0.968994140625</v>
+        <v>0.5854475498199463</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9103369116783142</v>
+        <v>0.9290764927864075</v>
       </c>
       <c r="I110" t="n">
-        <v>0.137030303478241</v>
+        <v>0.2643281221389771</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4620,16 +4632,16 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D111" t="n">
         <v>15</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9273141026496887</v>
+        <v>0.9231093525886536</v>
       </c>
       <c r="F111" t="n">
-        <v>0.004379040561616421</v>
+        <v>0.003423789516091347</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4637,10 +4649,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.9332300424575806</v>
+        <v>0.9463032484054565</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3047800660133362</v>
+        <v>0.4682199060916901</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D112" t="n">
         <v>15</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9608256816864014</v>
+        <v>0.9614101648330688</v>
       </c>
       <c r="F112" t="n">
-        <v>0.09626677632331848</v>
+        <v>0.108286090195179</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,10 +4687,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.950154185295105</v>
+        <v>0.9370697736740112</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5268831849098206</v>
+        <v>0.3469505310058594</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D113" t="n">
         <v>15</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9403420686721802</v>
+        <v>0.9392876625061035</v>
       </c>
       <c r="F113" t="n">
-        <v>0.01389930211007595</v>
+        <v>0.01386937964707613</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,14 +4725,14 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.8750943541526794</v>
+        <v>0.8955024480819702</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0401119664311409</v>
+        <v>0.08127230405807495</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4746,16 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D114" t="n">
         <v>15</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9163800477981567</v>
+        <v>0.9006227254867554</v>
       </c>
       <c r="F114" t="n">
-        <v>0.001748967915773392</v>
+        <v>0.0005757699836976826</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4751,10 +4763,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.8382320404052734</v>
+        <v>0.821195125579834</v>
       </c>
       <c r="I114" t="n">
-        <v>0.01188432704657316</v>
+        <v>0.006968440487980843</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D115" t="n">
         <v>15</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9798741936683655</v>
+        <v>0.9794318675994873</v>
       </c>
       <c r="F115" t="n">
-        <v>0.54667067527771</v>
+        <v>0.541675329208374</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9590379595756531</v>
+        <v>0.9235466718673706</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6756789684295654</v>
+        <v>0.2181238830089569</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4810,16 +4822,16 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D116" t="n">
         <v>15</v>
       </c>
       <c r="E116" t="n">
-        <v>0.943290114402771</v>
+        <v>0.9461231231689453</v>
       </c>
       <c r="F116" t="n">
-        <v>0.01821746677160263</v>
+        <v>0.02579554729163647</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4827,10 +4839,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9102765321731567</v>
+        <v>0.9260491132736206</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1367384344339371</v>
+        <v>0.2380072176456451</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D117" t="n">
         <v>15</v>
       </c>
       <c r="E117" t="n">
-        <v>0.97528475522995</v>
+        <v>0.9726184010505676</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3741694390773773</v>
+        <v>0.3068424463272095</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,10 +4877,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.9168792963027954</v>
+        <v>0.9274696707725525</v>
       </c>
       <c r="I117" t="n">
-        <v>0.172606959939003</v>
+        <v>0.2500396072864532</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D118" t="n">
         <v>15</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9646567106246948</v>
+        <v>0.9586564302444458</v>
       </c>
       <c r="F118" t="n">
-        <v>0.13926100730896</v>
+        <v>0.08340678364038467</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4903,10 +4915,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9038046598434448</v>
+        <v>0.9028542041778564</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1088176742196083</v>
+        <v>0.1052328422665596</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4924,16 +4936,16 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D119" t="n">
         <v>15</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9444650411605835</v>
+        <v>0.9420074224472046</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0203098226338625</v>
+        <v>0.01771830394864082</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4941,10 +4953,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9468621015548706</v>
+        <v>0.9143179059028625</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4764551818370819</v>
+        <v>0.1577039957046509</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D120" t="n">
         <v>15</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8909614682197571</v>
+        <v>0.8932611346244812</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0002449187159072608</v>
+        <v>0.000333447300363332</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.8931058645248413</v>
+        <v>0.8994008898735046</v>
       </c>
       <c r="I120" t="n">
-        <v>0.07473419606685638</v>
+        <v>0.0931890532374382</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D121" t="n">
         <v>15</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9756697416305542</v>
+        <v>0.9796867370605469</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3869225680828094</v>
+        <v>0.5521981716156006</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.8804753422737122</v>
+        <v>0.8312088251113892</v>
       </c>
       <c r="I121" t="n">
-        <v>0.04822677373886108</v>
+        <v>0.009516051970422268</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
